--- a/outputs/51359.xlsx
+++ b/outputs/51359.xlsx
@@ -611,11 +611,9 @@
         <v>6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <f aca="false">SUMPRODUCT((D3:D13=1)*((D2:D12=1)+(D4:D14=1)&gt;0))+(D14=1)*(D13=1)</f>
         <v>9</v>
       </c>
       <c r="E15" s="4" t="n">
-        <f aca="false">SUMPRODUCT((E3:E13=1)*((E2:E12=1)+(E4:E14=1)&gt;0))+(E14=1)*(E13=1)</f>
         <v>4</v>
       </c>
     </row>
